--- a/tests/integration_workspace/dashboard_full_pipeline/output/PRICE_HISTORY.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/PRICE_HISTORY.xlsx
@@ -484,7 +484,11 @@
           <t>SKU-APPLE</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SVO shampoo apple 1 l</t>
+        </is>
+      </c>
       <c r="C2" t="n">
         <v>35.5</v>
       </c>
@@ -493,7 +497,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -509,7 +513,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -522,7 +526,11 @@
           <t>SKU-LIME</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SVO shampoo lime 1 l</t>
+        </is>
+      </c>
       <c r="C3" t="n">
         <v>39</v>
       </c>
@@ -531,7 +539,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -547,7 +555,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
       <c r="L3" t="n">

--- a/tests/integration_workspace/dashboard_full_pipeline/output/PRICE_HISTORY.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/PRICE_HISTORY.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
       <c r="L3" t="n">
